--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>sources &amp; uses; summary; general info; budget</t>
+          <t>sources &amp; uses; summary; general info; inputs; budget</t>
         </is>
       </c>
       <c r="Q6" t="b">
@@ -968,12 +968,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>sources &amp; uses; inputs; debt; debt information; summary; general info</t>
+        </is>
+      </c>
       <c r="Q7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1039,12 +1049,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>sources &amp; uses; inputs; summary; general info; one pager</t>
+        </is>
+      </c>
       <c r="Q8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,21 @@
           <t>applies_to_property_types</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>source_primary</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>source_forbidden</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,6 +615,21 @@
       <c r="Q2" t="b">
         <v>1</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>summary; sources_uses; inputs</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>cash_flow; debt; comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -667,7 +697,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -738,7 +767,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -823,6 +851,21 @@
       <c r="Q5" t="b">
         <v>1</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>capex; sources_uses; summary</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -904,6 +947,21 @@
       <c r="Q6" t="b">
         <v>1</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>sources_uses; summary; inputs</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>cash_flow; comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -985,6 +1043,21 @@
       <c r="Q7" t="b">
         <v>1</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>sources_uses; debt; summary</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1066,6 +1139,21 @@
       <c r="Q8" t="b">
         <v>1</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>sources_uses; summary; inputs</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1133,7 +1221,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1204,7 +1291,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1289,6 +1375,21 @@
       <c r="Q11" t="b">
         <v>1</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1356,7 +1457,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1427,7 +1527,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1498,7 +1597,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1667,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1640,7 +1737,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1711,7 +1807,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1877,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1853,7 +1947,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1938,6 +2031,21 @@
       <c r="Q20" t="b">
         <v>1</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>summary; cash_flow; inputs</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2005,7 +2113,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -2076,7 +2183,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -2147,7 +2253,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -2218,7 +2323,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2289,7 +2393,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2463,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2431,7 +2533,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2502,7 +2603,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2573,7 +2673,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2644,7 +2743,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2729,6 +2827,21 @@
       <c r="Q31" t="b">
         <v>1</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>summary; inputs; cash_flow</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2796,7 +2909,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2867,7 +2979,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2938,7 +3049,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3119,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3189,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -3151,7 +3259,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -3222,7 +3329,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -3293,7 +3399,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -3364,7 +3469,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -3435,7 +3539,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3506,7 +3609,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3557,7 +3659,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3628,7 +3729,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3699,7 +3799,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3770,7 +3869,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3841,7 +3939,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3912,7 +4009,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3983,7 +4079,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -4054,7 +4149,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -4125,7 +4219,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -4196,7 +4289,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -4267,7 +4359,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -4338,7 +4429,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -4409,7 +4499,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -4480,7 +4569,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -4551,7 +4639,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4622,7 +4709,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4693,7 +4779,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4778,6 +4863,21 @@
       <c r="Q60" t="b">
         <v>1</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>debt; sources_uses; summary</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4845,7 +4945,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4916,7 +5015,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -5001,6 +5099,21 @@
       <c r="Q63" t="b">
         <v>1</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>debt; summary</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5082,6 +5195,21 @@
       <c r="Q64" t="b">
         <v>1</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>debt; summary; returns</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5163,6 +5291,21 @@
       <c r="Q65" t="b">
         <v>1</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>debt; inputs; summary</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5230,7 +5373,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -5315,6 +5457,21 @@
       <c r="Q67" t="b">
         <v>1</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>debt; inputs</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5396,6 +5553,21 @@
       <c r="Q68" t="b">
         <v>1</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>debt; inputs</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5463,7 +5635,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -5534,7 +5705,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -5605,7 +5775,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -5676,7 +5845,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -5747,7 +5915,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5818,7 +5985,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5889,7 +6055,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5974,6 +6139,21 @@
       <c r="Q76" t="b">
         <v>1</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>summary; returns</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6055,6 +6235,21 @@
       <c r="Q77" t="b">
         <v>1</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>returns</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>returns; summary</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6136,6 +6331,21 @@
       <c r="Q78" t="b">
         <v>1</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>returns</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>returns; summary</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6217,6 +6427,21 @@
       <c r="Q79" t="b">
         <v>1</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>returns</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>returns; summary</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6284,7 +6509,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -6355,7 +6579,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -6426,7 +6649,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -6497,7 +6719,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -6568,7 +6789,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -6639,7 +6859,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -6710,7 +6929,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -6781,7 +6999,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -6847,7 +7064,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -6913,7 +7129,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6979,7 +7194,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -7045,7 +7259,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -7111,7 +7324,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -7196,6 +7408,21 @@
       <c r="Q93" t="b">
         <v>1</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>summary; returns; inputs</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7272,6 +7499,21 @@
       <c r="Q94" t="b">
         <v>1</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7348,6 +7590,21 @@
       <c r="Q95" t="b">
         <v>1</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7429,6 +7686,21 @@
           <t>Office; Multifamily; Industrial; Retail; Mixed-use; Self-Storage; Senior Living</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7491,7 +7763,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -7557,7 +7828,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -7623,7 +7893,6 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -7697,6 +7966,21 @@
       <c r="Q100" t="b">
         <v>1</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow; debt</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7767,6 +8051,21 @@
       <c r="Q101" t="b">
         <v>1</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow; debt</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7837,6 +8136,21 @@
       <c r="Q102" t="b">
         <v>1</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow; debt</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7913,6 +8227,21 @@
       <c r="Q103" t="b">
         <v>1</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7989,6 +8318,21 @@
       <c r="Q104" t="b">
         <v>1</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>summary; returns; cash_flow</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8065,6 +8409,21 @@
       <c r="Q105" t="b">
         <v>1</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8135,6 +8494,21 @@
       <c r="Q106" t="b">
         <v>1</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>summary; inputs</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market; cash_flow</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8205,6 +8579,21 @@
       <c r="Q107" t="b">
         <v>1</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>deal_basis</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>summary; returns; inputs</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8281,6 +8670,21 @@
       <c r="Q108" t="b">
         <v>1</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>debt; inputs</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8356,6 +8760,21 @@
       </c>
       <c r="Q109" t="b">
         <v>1</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>debt; inputs</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
       </c>
     </row>
   </sheetData>
